--- a/data/mpg/mpg_round_of_16_top5_bets.xlsx
+++ b/data/mpg/mpg_round_of_16_top5_bets.xlsx
@@ -121,12 +121,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -139,45 +139,45 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I2">
-        <v>0.4118092801729689</v>
+        <v>0.5380999687640712</v>
       </c>
       <c r="J2">
-        <v>93.0</v>
+        <v>72.0</v>
       </c>
       <c r="K2">
-        <v>38.29826305608611</v>
+        <v>38.74319775101313</v>
       </c>
       <c r="L2">
-        <v>0.11422362090632592</v>
+        <v>0.11756760952254773</v>
       </c>
       <c r="M2">
-        <v>0.2536062895934641</v>
+        <v>0.20618884309169183</v>
       </c>
       <c r="N2">
-        <v>0.20042266577091816</v>
+        <v>0.18484053002759276</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="P2">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="Q2">
-        <v>3.4267086271897775</v>
+        <v>5.878380476127386</v>
       </c>
       <c r="R2">
-        <v>41.72497168327588</v>
+        <v>44.62157822714052</v>
       </c>
     </row>
     <row r="3">
@@ -193,12 +193,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -211,45 +211,45 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I3">
-        <v>0.4118092801729689</v>
+        <v>0.5380999687640712</v>
       </c>
       <c r="J3">
-        <v>93.0</v>
+        <v>72.0</v>
       </c>
       <c r="K3">
-        <v>38.29826305608611</v>
+        <v>38.74319775101313</v>
       </c>
       <c r="L3">
-        <v>0.10430804240335688</v>
+        <v>0.1007209068755276</v>
       </c>
       <c r="M3">
-        <v>0.23159111398129412</v>
+        <v>0.17664327231071378</v>
       </c>
       <c r="N3">
-        <v>0.20590231445291696</v>
+        <v>0.14075914568903103</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="P3">
-        <v>30.0</v>
+        <v>50.0</v>
       </c>
       <c r="Q3">
-        <v>3.1292412721007064</v>
+        <v>5.0360453437763795</v>
       </c>
       <c r="R3">
-        <v>41.427504328186814</v>
+        <v>43.77924309478951</v>
       </c>
     </row>
     <row r="4">
@@ -265,12 +265,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -283,45 +283,45 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="I4">
-        <v>0.4118092801729689</v>
+        <v>0.5380999687640712</v>
       </c>
       <c r="J4">
-        <v>93.0</v>
+        <v>72.0</v>
       </c>
       <c r="K4">
-        <v>38.29826305608611</v>
+        <v>38.74319775101313</v>
       </c>
       <c r="L4">
-        <v>0.11144923628224387</v>
+        <v>0.043759627092679776</v>
       </c>
       <c r="M4">
-        <v>0.247446430670802</v>
+        <v>0.07674517599707653</v>
       </c>
       <c r="N4">
-        <v>0.3666648509834928</v>
+        <v>0.03822175502281931</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="P4">
-        <v>20.0</v>
+        <v>70.0</v>
       </c>
       <c r="Q4">
-        <v>2.2289847256448776</v>
+        <v>3.0631738964875845</v>
       </c>
       <c r="R4">
-        <v>40.527247781730985</v>
+        <v>41.80637164750071</v>
       </c>
     </row>
     <row r="5">
@@ -337,12 +337,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -355,45 +355,45 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I5">
-        <v>0.4118092801729689</v>
+        <v>0.5380999687640712</v>
       </c>
       <c r="J5">
-        <v>93.0</v>
+        <v>72.0</v>
       </c>
       <c r="K5">
-        <v>38.29826305608611</v>
+        <v>38.74319775101313</v>
       </c>
       <c r="L5">
-        <v>0.02594021304078892</v>
+        <v>0.13560663736966452</v>
       </c>
       <c r="M5">
-        <v>0.05759405216136108</v>
+        <v>0.23782550132945662</v>
       </c>
       <c r="N5">
-        <v>0.028447523633072156</v>
+        <v>0.355336003803286</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="P5">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="Q5">
-        <v>1.8158149128552246</v>
+        <v>2.7121327473932904</v>
       </c>
       <c r="R5">
-        <v>40.11407796894133</v>
+        <v>41.45533049840642</v>
       </c>
     </row>
     <row r="6">
@@ -409,12 +409,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -427,7 +427,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -436,22 +436,22 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.4118092801729689</v>
+        <v>0.5380999687640712</v>
       </c>
       <c r="J6">
-        <v>93.0</v>
+        <v>72.0</v>
       </c>
       <c r="K6">
-        <v>38.29826305608611</v>
+        <v>38.74319775101313</v>
       </c>
       <c r="L6">
-        <v>0.03225926112937355</v>
+        <v>0.05007078347065907</v>
       </c>
       <c r="M6">
-        <v>0.0716239903369584</v>
+        <v>0.08781361599879942</v>
       </c>
       <c r="N6">
-        <v>0.07429244289677273</v>
+        <v>0.09184186493824675</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -462,31 +462,31 @@
         <v>50.0</v>
       </c>
       <c r="Q6">
-        <v>1.6129630564686774</v>
+        <v>2.5035391735329533</v>
       </c>
       <c r="R6">
-        <v>39.911226112554786</v>
+        <v>41.246736924546084</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -499,31 +499,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I7">
-        <v>0.5392163817409323</v>
+        <v>0.4085510812463896</v>
       </c>
       <c r="J7">
-        <v>72.0</v>
+        <v>95.0</v>
       </c>
       <c r="K7">
-        <v>38.823579485347125</v>
+        <v>38.81235271840701</v>
       </c>
       <c r="L7">
-        <v>0.11810359324596491</v>
+        <v>0.08968476536446185</v>
       </c>
       <c r="M7">
-        <v>0.20765737857902072</v>
+        <v>0.2193033807046864</v>
       </c>
       <c r="N7">
-        <v>0.18593633098845236</v>
+        <v>0.18104812067330103</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -534,31 +534,31 @@
         <v>50.0</v>
       </c>
       <c r="Q7">
-        <v>5.905179662298245</v>
+        <v>4.484238268223092</v>
       </c>
       <c r="R7">
-        <v>44.72875914764537</v>
+        <v>43.29659098663011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -571,31 +571,31 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I8">
-        <v>0.5392163817409323</v>
+        <v>0.4085510812463896</v>
       </c>
       <c r="J8">
-        <v>72.0</v>
+        <v>95.0</v>
       </c>
       <c r="K8">
-        <v>38.823579485347125</v>
+        <v>38.81235271840701</v>
       </c>
       <c r="L8">
-        <v>0.10357540212000624</v>
+        <v>0.06750621621377584</v>
       </c>
       <c r="M8">
-        <v>0.18211297301272655</v>
+        <v>0.16507086096619114</v>
       </c>
       <c r="N8">
-        <v>0.14494567182023393</v>
+        <v>0.15331040585101105</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -606,31 +606,31 @@
         <v>50.0</v>
       </c>
       <c r="Q8">
-        <v>5.178770106000312</v>
+        <v>3.375310810688792</v>
       </c>
       <c r="R8">
-        <v>44.00234959134744</v>
+        <v>42.18766352909581</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -643,66 +643,66 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="I9">
-        <v>0.5392163817409323</v>
+        <v>0.4085510812463896</v>
       </c>
       <c r="J9">
-        <v>72.0</v>
+        <v>95.0</v>
       </c>
       <c r="K9">
-        <v>38.823579485347125</v>
+        <v>38.81235271840701</v>
       </c>
       <c r="L9">
-        <v>0.04295491625326249</v>
+        <v>0.041361625869321</v>
       </c>
       <c r="M9">
-        <v>0.07552611280553578</v>
+        <v>0.10114030345870592</v>
       </c>
       <c r="N9">
-        <v>0.037570027890751014</v>
+        <v>0.05218587433161824</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="P9">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="Q9">
-        <v>3.006844137728374</v>
+        <v>2.06808129346605</v>
       </c>
       <c r="R9">
-        <v>41.8304236230755</v>
+        <v>40.880434011873064</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -715,31 +715,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I10">
-        <v>0.5392163817409323</v>
+        <v>0.4085510812463896</v>
       </c>
       <c r="J10">
-        <v>72.0</v>
+        <v>95.0</v>
       </c>
       <c r="K10">
-        <v>38.823579485347125</v>
+        <v>38.81235271840701</v>
       </c>
       <c r="L10">
-        <v>0.13618331666747474</v>
+        <v>0.0943978370060609</v>
       </c>
       <c r="M10">
-        <v>0.23944631800041066</v>
+        <v>0.23082810890468486</v>
       </c>
       <c r="N10">
-        <v>0.3573335570218977</v>
+        <v>0.35730464329948824</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -750,31 +750,31 @@
         <v>20.0</v>
       </c>
       <c r="Q10">
-        <v>2.723666333349495</v>
+        <v>1.887956740121218</v>
       </c>
       <c r="R10">
-        <v>41.54724581869662</v>
+        <v>40.70030945852823</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -787,45 +787,45 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="I11">
-        <v>0.5392163817409323</v>
+        <v>0.4085510812463896</v>
       </c>
       <c r="J11">
-        <v>72.0</v>
+        <v>95.0</v>
       </c>
       <c r="K11">
-        <v>38.823579485347125</v>
+        <v>38.81235271840701</v>
       </c>
       <c r="L11">
-        <v>0.04910180255487713</v>
+        <v>0.022213626343429996</v>
       </c>
       <c r="M11">
-        <v>0.08633396598539828</v>
+        <v>0.05431829291215664</v>
       </c>
       <c r="N11">
-        <v>0.09018729705470721</v>
+        <v>0.028026884544391156</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="P11">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="Q11">
-        <v>2.4550901277438566</v>
+        <v>1.5549538440400998</v>
       </c>
       <c r="R11">
-        <v>41.27866961309098</v>
+        <v>40.36730656244711</v>
       </c>
     </row>
     <row r="12">
@@ -836,17 +836,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -859,45 +859,45 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="I12">
-        <v>0.3833772547240082</v>
+        <v>0.7660935064565033</v>
       </c>
       <c r="J12">
-        <v>100.0</v>
+        <v>43.0</v>
       </c>
       <c r="K12">
-        <v>38.33772547240082</v>
+        <v>32.942020777629644</v>
       </c>
       <c r="L12">
-        <v>0.07929725788892006</v>
+        <v>0.1885270255353901</v>
       </c>
       <c r="M12">
-        <v>0.1850693777681561</v>
+        <v>0.24761396609341538</v>
       </c>
       <c r="N12">
-        <v>0.16559478317367451</v>
+        <v>0.20342024139267179</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="P12">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="Q12">
-        <v>3.9648628944460027</v>
+        <v>5.655810766061704</v>
       </c>
       <c r="R12">
-        <v>42.30258836684682</v>
+        <v>38.59783154369135</v>
       </c>
     </row>
     <row r="13">
@@ -908,17 +908,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -931,45 +931,45 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="I13">
-        <v>0.3833772547240082</v>
+        <v>0.7660935064565033</v>
       </c>
       <c r="J13">
-        <v>100.0</v>
+        <v>43.0</v>
       </c>
       <c r="K13">
-        <v>38.33772547240082</v>
+        <v>32.942020777629644</v>
       </c>
       <c r="L13">
-        <v>0.07680562142794965</v>
+        <v>0.16758941267391056</v>
       </c>
       <c r="M13">
-        <v>0.17925422574736127</v>
+        <v>0.22011421985577986</v>
       </c>
       <c r="N13">
-        <v>0.14257026804911083</v>
+        <v>0.20343217912493058</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="P13">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="Q13">
-        <v>3.8402810713974826</v>
+        <v>5.027682380217317</v>
       </c>
       <c r="R13">
-        <v>42.178006543798304</v>
+        <v>37.96970315784696</v>
       </c>
     </row>
     <row r="14">
@@ -980,17 +980,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1003,45 +1003,45 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="I14">
-        <v>0.3833772547240082</v>
+        <v>0.7660935064565033</v>
       </c>
       <c r="J14">
-        <v>100.0</v>
+        <v>43.0</v>
       </c>
       <c r="K14">
-        <v>38.33772547240082</v>
+        <v>32.942020777629644</v>
       </c>
       <c r="L14">
-        <v>0.041805105169585695</v>
+        <v>0.07194089512845621</v>
       </c>
       <c r="M14">
-        <v>0.09756762096496902</v>
+        <v>0.09448815264803274</v>
       </c>
       <c r="N14">
-        <v>0.048500397326387876</v>
+        <v>0.10673309060480798</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="P14">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="Q14">
-        <v>2.926357361870999</v>
+        <v>3.5970447564228105</v>
       </c>
       <c r="R14">
-        <v>41.26408283427182</v>
+        <v>36.539065534052455</v>
       </c>
     </row>
     <row r="15">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1075,45 +1075,45 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="I15">
-        <v>0.3833772547240082</v>
+        <v>0.7660935064565033</v>
       </c>
       <c r="J15">
-        <v>100.0</v>
+        <v>43.0</v>
       </c>
       <c r="K15">
-        <v>38.33772547240082</v>
+        <v>32.942020777629644</v>
       </c>
       <c r="L15">
-        <v>0.11594128498048058</v>
+        <v>0.11890658060338409</v>
       </c>
       <c r="M15">
-        <v>0.2705917208264038</v>
+        <v>0.15617352437506798</v>
       </c>
       <c r="N15">
-        <v>0.40352954730822915</v>
+        <v>0.24056238018952844</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Exact</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="P15">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="Q15">
-        <v>2.3188256996096115</v>
+        <v>3.567197418101523</v>
       </c>
       <c r="R15">
-        <v>40.65655117201043</v>
+        <v>36.509218195731165</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1147,45 +1147,45 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="I16">
-        <v>0.37911299830891587</v>
+        <v>0.7660935064565033</v>
       </c>
       <c r="J16">
-        <v>95.0</v>
+        <v>43.0</v>
       </c>
       <c r="K16">
-        <v>36.015734839347004</v>
+        <v>32.942020777629644</v>
       </c>
       <c r="L16">
-        <v>0.08872914447009403</v>
+        <v>0.041215425011505054</v>
       </c>
       <c r="M16">
-        <v>0.23302284769383114</v>
+        <v>0.054132901223802245</v>
       </c>
       <c r="N16">
-        <v>0.19175055231618368</v>
+        <v>0.027794594969648242</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="P16">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="Q16">
-        <v>4.436457223504702</v>
+        <v>2.8850797508053536</v>
       </c>
       <c r="R16">
-        <v>40.45219206285171</v>
+        <v>35.827100528435</v>
       </c>
     </row>
     <row r="17">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1219,45 +1219,45 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="I17">
-        <v>0.7600797048291267</v>
+        <v>0.4365937218548486</v>
       </c>
       <c r="J17">
-        <v>43.0</v>
+        <v>85.0</v>
       </c>
       <c r="K17">
-        <v>32.683427307652444</v>
+        <v>37.11046635766213</v>
       </c>
       <c r="L17">
-        <v>0.1828276696217703</v>
+        <v>0.1231642459713582</v>
       </c>
       <c r="M17">
-        <v>0.2421942897488518</v>
+        <v>0.2583220574899055</v>
       </c>
       <c r="N17">
-        <v>0.19895355002543058</v>
+        <v>0.20459703580000643</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="P17">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="Q17">
-        <v>9.141383481088514</v>
+        <v>3.6949273791407458</v>
       </c>
       <c r="R17">
-        <v>41.82481078874096</v>
+        <v>40.80539373680288</v>
       </c>
     </row>
     <row r="18">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1291,31 +1291,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="I18">
-        <v>0.7600797048291267</v>
+        <v>0.4365937218548486</v>
       </c>
       <c r="J18">
-        <v>43.0</v>
+        <v>85.0</v>
       </c>
       <c r="K18">
-        <v>32.683427307652444</v>
+        <v>37.11046635766213</v>
       </c>
       <c r="L18">
-        <v>0.16361068517321498</v>
+        <v>0.11452527818174013</v>
       </c>
       <c r="M18">
-        <v>0.2167372902188508</v>
+        <v>0.24020287106203483</v>
       </c>
       <c r="N18">
-        <v>0.20029677423950876</v>
+        <v>0.21402699937207995</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
         <v>30.0</v>
       </c>
       <c r="Q18">
-        <v>4.9083205551964495</v>
+        <v>3.435758345452204</v>
       </c>
       <c r="R18">
-        <v>37.59174786284889</v>
+        <v>40.54622470311434</v>
       </c>
     </row>
     <row r="19">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1363,45 +1363,45 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="I19">
-        <v>0.7600797048291267</v>
+        <v>0.4365937218548486</v>
       </c>
       <c r="J19">
-        <v>43.0</v>
+        <v>85.0</v>
       </c>
       <c r="K19">
-        <v>32.683427307652444</v>
+        <v>37.11046635766213</v>
       </c>
       <c r="L19">
-        <v>0.11997337359496882</v>
+        <v>0.11326503163581086</v>
       </c>
       <c r="M19">
-        <v>0.15893035264694508</v>
+        <v>0.23755965688797412</v>
       </c>
       <c r="N19">
-        <v>0.24479126266786713</v>
+        <v>0.3527863781060783</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Exact</t>
         </is>
       </c>
       <c r="P19">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="Q19">
-        <v>3.5992012078490645</v>
+        <v>2.265300632716217</v>
       </c>
       <c r="R19">
-        <v>36.28262851550151</v>
+        <v>39.37576699037835</v>
       </c>
     </row>
     <row r="20">
@@ -1412,17 +1412,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1435,45 +1435,45 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="I20">
-        <v>0.7600797048291267</v>
+        <v>0.4365937218548486</v>
       </c>
       <c r="J20">
-        <v>43.0</v>
+        <v>85.0</v>
       </c>
       <c r="K20">
-        <v>32.683427307652444</v>
+        <v>37.11046635766213</v>
       </c>
       <c r="L20">
-        <v>0.07042754580099046</v>
+        <v>0.02485539574437893</v>
       </c>
       <c r="M20">
-        <v>0.09329632363259377</v>
+        <v>0.05213117587637355</v>
       </c>
       <c r="N20">
-        <v>0.10537923030359865</v>
+        <v>0.025805684580118615</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Tres rare</t>
+          <t>Mega rare</t>
         </is>
       </c>
       <c r="P20">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="Q20">
-        <v>3.5213772900495233</v>
+        <v>1.739877702106525</v>
       </c>
       <c r="R20">
-        <v>36.204804597701965</v>
+        <v>38.85034405976866</v>
       </c>
     </row>
     <row r="21">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1507,408 +1507,48 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="I21">
-        <v>0.7600797048291267</v>
+        <v>0.4365937218548486</v>
       </c>
       <c r="J21">
-        <v>43.0</v>
+        <v>85.0</v>
       </c>
       <c r="K21">
-        <v>32.683427307652444</v>
+        <v>37.11046635766213</v>
       </c>
       <c r="L21">
-        <v>0.04205683810462272</v>
+        <v>0.0333786772253962</v>
       </c>
       <c r="M21">
-        <v>0.05571326295906936</v>
+        <v>0.0700077243127924</v>
       </c>
       <c r="N21">
-        <v>0.028603976018337675</v>
+        <v>0.0727751516242672</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Mega rare</t>
+          <t>Tres rare</t>
         </is>
       </c>
       <c r="P21">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="Q21">
-        <v>2.94397866732359</v>
+        <v>1.66893386126981</v>
       </c>
       <c r="R21">
-        <v>35.627405974976035</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>elimination</t>
-        </is>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I22">
-        <v>0.4391282167450133</v>
-      </c>
-      <c r="J22">
-        <v>85.0</v>
-      </c>
-      <c r="K22">
-        <v>37.32589842332613</v>
-      </c>
-      <c r="L22">
-        <v>0.12330564153099352</v>
-      </c>
-      <c r="M22">
-        <v>0.25761300307131224</v>
-      </c>
-      <c r="N22">
-        <v>0.2040495674920334</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="P22">
-        <v>30.0</v>
-      </c>
-      <c r="Q22">
-        <v>3.699169245929806</v>
-      </c>
-      <c r="R22">
-        <v>41.02506766925593</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>elimination</t>
-        </is>
-      </c>
-      <c r="F23">
-        <v>2</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="I23">
-        <v>0.4391282167450133</v>
-      </c>
-      <c r="J23">
-        <v>85.0</v>
-      </c>
-      <c r="K23">
-        <v>37.32589842332613</v>
-      </c>
-      <c r="L23">
-        <v>0.11506328295413562</v>
-      </c>
-      <c r="M23">
-        <v>0.24039287657092628</v>
-      </c>
-      <c r="N23">
-        <v>0.21421112151215949</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="P23">
-        <v>30.0</v>
-      </c>
-      <c r="Q23">
-        <v>3.4518984886240687</v>
-      </c>
-      <c r="R23">
-        <v>40.7777969119502</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>elimination</t>
-        </is>
-      </c>
-      <c r="F24">
-        <v>3</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="I24">
-        <v>0.4391282167450133</v>
-      </c>
-      <c r="J24">
-        <v>85.0</v>
-      </c>
-      <c r="K24">
-        <v>37.32589842332613</v>
-      </c>
-      <c r="L24">
-        <v>0.11352661640126022</v>
-      </c>
-      <c r="M24">
-        <v>0.2371824372066741</v>
-      </c>
-      <c r="N24">
-        <v>0.3522505644493637</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Exact</t>
-        </is>
-      </c>
-      <c r="P24">
-        <v>20.0</v>
-      </c>
-      <c r="Q24">
-        <v>2.2705323280252045</v>
-      </c>
-      <c r="R24">
-        <v>39.596430751351335</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>elimination</t>
-        </is>
-      </c>
-      <c r="F25">
-        <v>4</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="I25">
-        <v>0.4391282167450133</v>
-      </c>
-      <c r="J25">
-        <v>85.0</v>
-      </c>
-      <c r="K25">
-        <v>37.32589842332613</v>
-      </c>
-      <c r="L25">
-        <v>0.02494163842477152</v>
-      </c>
-      <c r="M25">
-        <v>0.05210864885293342</v>
-      </c>
-      <c r="N25">
-        <v>0.025796318349301153</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Mega rare</t>
-        </is>
-      </c>
-      <c r="P25">
-        <v>70.0</v>
-      </c>
-      <c r="Q25">
-        <v>1.7459146897340063</v>
-      </c>
-      <c r="R25">
-        <v>39.07181311306014</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>elimination</t>
-        </is>
-      </c>
-      <c r="F26">
-        <v>5</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="I26">
-        <v>0.4391282167450133</v>
-      </c>
-      <c r="J26">
-        <v>85.0</v>
-      </c>
-      <c r="K26">
-        <v>37.32589842332613</v>
-      </c>
-      <c r="L26">
-        <v>0.03357442184511748</v>
-      </c>
-      <c r="M26">
-        <v>0.07014445998182296</v>
-      </c>
-      <c r="N26">
-        <v>0.07292233834347484</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Tres rare</t>
-        </is>
-      </c>
-      <c r="P26">
-        <v>50.0</v>
-      </c>
-      <c r="Q26">
-        <v>1.6787210922558742</v>
-      </c>
-      <c r="R26">
-        <v>39.00461951558201</v>
+        <v>38.77940021893194</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R26"/>
+  <autoFilter ref="A1:R21"/>
 </worksheet>
 </file>